--- a/sample_mizan_period1.xlsx
+++ b/sample_mizan_period1.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>Hesap Kodu</t>
   </si>
@@ -40,21 +40,48 @@
     <t>153</t>
   </si>
   <si>
+    <t>254</t>
+  </si>
+  <si>
+    <t>300</t>
+  </si>
+  <si>
     <t>320</t>
   </si>
   <si>
+    <t>360</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
     <t>500</t>
   </si>
   <si>
+    <t>570</t>
+  </si>
+  <si>
     <t>600</t>
   </si>
   <si>
+    <t>611</t>
+  </si>
+  <si>
     <t>621</t>
   </si>
   <si>
+    <t>631</t>
+  </si>
+  <si>
     <t>632</t>
   </si>
   <si>
+    <t>660</t>
+  </si>
+  <si>
+    <t>691</t>
+  </si>
+  <si>
     <t>Kasa</t>
   </si>
   <si>
@@ -67,19 +94,46 @@
     <t>Ticari Mallar</t>
   </si>
   <si>
+    <t>Taşıtlar ve Demirbaşlar</t>
+  </si>
+  <si>
+    <t>Banka Kredileri (KV)</t>
+  </si>
+  <si>
     <t>Satıcılar</t>
   </si>
   <si>
+    <t>Ödenecek Vergi ve Fonlar</t>
+  </si>
+  <si>
+    <t>Banka Kredileri (UV)</t>
+  </si>
+  <si>
     <t>Sermaye</t>
   </si>
   <si>
+    <t>Geçmiş Yıllar Kârları</t>
+  </si>
+  <si>
     <t>Yurtiçi Satışlar</t>
   </si>
   <si>
+    <t>Satış İskontoları</t>
+  </si>
+  <si>
     <t>Satılan Ticari Mallar Maliyeti</t>
   </si>
   <si>
+    <t>Pazarlama Satış Dağıtım Giderleri</t>
+  </si>
+  <si>
     <t>Genel Yönetim Giderleri</t>
+  </si>
+  <si>
+    <t>Finansman Giderleri</t>
+  </si>
+  <si>
+    <t>Dönem Kârı Vergi Karşılığı</t>
   </si>
 </sst>
 </file>
@@ -437,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -459,10 +513,10 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C2">
-        <v>90000</v>
+        <v>70000</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -473,10 +527,10 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C3">
-        <v>350000</v>
+        <v>260000</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -487,10 +541,10 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C4">
-        <v>200000</v>
+        <v>210000</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -501,10 +555,10 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C5">
-        <v>180000</v>
+        <v>190000</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -515,13 +569,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="D6">
-        <v>128600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -529,13 +583,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <v>300000</v>
+        <v>180000</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -543,13 +597,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>800000</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -557,13 +611,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C9">
-        <v>205000</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -571,12 +625,138 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>92000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14">
+        <v>8000</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15">
+        <v>480000</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16">
+        <v>95000</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17">
+        <v>90000</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18">
+        <v>35000</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
         <v>21</v>
       </c>
-      <c r="C10">
-        <v>61700</v>
-      </c>
-      <c r="D10">
+      <c r="B19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19">
+        <v>12000</v>
+      </c>
+      <c r="D19">
         <v>0</v>
       </c>
     </row>
